--- a/PRP申請書類 自動転記ツール/01_input【ヒアリングシートをここへ】/PRPヒアリングシート0707テスト.xlsx
+++ b/PRP申請書類 自動転記ツール/01_input【ヒアリングシートをここへ】/PRPヒアリングシート0707テスト.xlsx
@@ -1,31 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="7" rupBuild="9303"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\マイドライブ\01.グローアップコンサルティング事務所\00.営業案件\再生医療案件\■サンプルデータ\PRP提供計画資料（関節・筋腱靭帯）\泉山確認用\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{382C5D6E-F052-4E4B-BF37-8138D3A99E28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1335" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15756" yWindow="-16200" windowWidth="14616" windowHeight="13176"/>
   </bookViews>
   <sheets>
     <sheet name="ヒアリングシート（PRP）" sheetId="1" r:id="rId1"/>
-    <sheet name="略歴書（PRP）" sheetId="2" r:id="rId2"/>
-    <sheet name="カテゴリ・治療名" sheetId="3" r:id="rId3"/>
-    <sheet name="PRPメーカー" sheetId="4" r:id="rId4"/>
-    <sheet name="審査委員会" sheetId="5" r:id="rId5"/>
-    <sheet name="培養委託先" sheetId="6" r:id="rId6"/>
-    <sheet name="Sheet6" sheetId="7" r:id="rId7"/>
+    <sheet name="カテゴリ・治療名" sheetId="3" r:id="rId2"/>
+    <sheet name="PRPメーカー" sheetId="4" r:id="rId3"/>
+    <sheet name="審査委員会" sheetId="5" r:id="rId4"/>
+    <sheet name="培養委託先" sheetId="6" r:id="rId5"/>
+    <sheet name="Sheet6" sheetId="7" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'ヒアリングシート（PRP）'!$A$1:$C$100</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'ヒアリングシート（PRP）'!$A$1:$C$114</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'ヒアリングシート（PRP）'!$2:$2</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="145621"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -43,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="382" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="361" uniqueCount="286">
   <si>
     <t>【医療機関様用】ヒアリングシート・必要書類リスト</t>
   </si>
@@ -73,12 +66,6 @@
   </si>
   <si>
     <t>医療機関/住所（診療所開設届上）</t>
-  </si>
-  <si>
-    <t>開設者（診療所開設届上）※医療法人の場合（役職も必要）</t>
-  </si>
-  <si>
-    <t>山中 次郎</t>
   </si>
   <si>
     <t>氏名</t>
@@ -122,27 +109,12 @@
     <t>自家多血小板血漿（PRP）を用いた関節内組織損傷に対する治療</t>
   </si>
   <si>
-    <t>上記治療費の設定（税別）</t>
-  </si>
-  <si>
-    <t>〇〇円/回　</t>
-  </si>
-  <si>
-    <t>PRPと幹細胞はソート自体を分ける</t>
-  </si>
-  <si>
     <t>再生医療②（右記タブから選択）</t>
   </si>
   <si>
     <t>四肢の筋・腱・靱帯及びその付着部の傷害を対象とした自家多血小板血漿（PRP）注入療法</t>
   </si>
   <si>
-    <t>カウンセリング費：〇〇円
-血液検査費：〇〇円
-1億cell：〇〇円/回
-2億cell：〇〇円/回</t>
-  </si>
-  <si>
     <t>再生医療③（右記タブから選択）</t>
   </si>
   <si>
@@ -185,21 +157,10 @@
     <t>採血・製造・投与の場所（PRPの場合）</t>
   </si>
   <si>
-    <t>PRP製造場所（細胞培養加工施設として届出するお部屋）
-※区画として区切られた部屋（カーテン等は原則不可）
-※通常：処置室が多い</t>
-  </si>
-  <si>
     <t>人員・診療時間等</t>
   </si>
   <si>
-    <t>再生医療を行う医師の氏名</t>
-  </si>
-  <si>
     <t>再生医療を行う医師（行が足りない場合は増やしてください）</t>
-  </si>
-  <si>
-    <t>製造責任者（通常、院長や再生医療をご担当される責任者）</t>
   </si>
   <si>
     <t>品質責任者（通常、院長や治療医師をサポートする看護師等）</t>
@@ -345,114 +306,6 @@
   <si>
     <t>HP制作担当者・管理業者
 ※再生医療関連の記事やページを掲載する場合の対応のため</t>
-  </si>
-  <si>
-    <t>医師略歴書
-（再生医療等を行う医師）</t>
-  </si>
-  <si>
-    <t>やまなか　じろう</t>
-  </si>
-  <si>
-    <t>生年月日</t>
-  </si>
-  <si>
-    <t>昭和〇〇年〇〇月○○日</t>
-  </si>
-  <si>
-    <t>所属</t>
-  </si>
-  <si>
-    <t>○○病院　整形外科</t>
-  </si>
-  <si>
-    <t>役職</t>
-  </si>
-  <si>
-    <t>整形外科センター長</t>
-  </si>
-  <si>
-    <t>医師免許
-職歴</t>
-  </si>
-  <si>
-    <t>医籍番号：第・・・・・号　　
-免許取得日：・・・年・・月・・日
-○○○○年　○○大学　医学部　卒
-20○○年4月～20○○年3月　○○病院　研修医　勤務
-20○○年4月～20○○年3月　○○病院　整形外科　勤務
-20○○年4月～20○○年3月　○○病院　整形外科　勤務
-20○○年4月～20○○年3月　○○病院　整形外科　勤務
-20○○年4月～20○○年3月　○○病院　整形外科　勤務
-20○○年4月～20○○年3月　○○病院　整形外科　勤務
-20○○年4月～20○○年3月　○○病院　整形外科　勤務
-20○○年4月～20○○年3月　○○病院　整形外科　勤務
-20○○年4月～20○○年3月　○○大学医学部附属病院　整形外科　勤務
-20○○年4月～　○○クリニック開業　院長着任　現在に至る</t>
-  </si>
-  <si>
-    <t>専門分野</t>
-  </si>
-  <si>
-    <t>膝関節、スポーツ医学、外傷全般</t>
-  </si>
-  <si>
-    <t>所属学会等</t>
-  </si>
-  <si>
-    <t>日本再生医療学会、日本整形外科学会、日本手外科学会、日本リウマチ学会、日本脊椎脊髄病学会</t>
-  </si>
-  <si>
-    <t>認定医等の資格</t>
-  </si>
-  <si>
-    <t>日本整形外科学会専門医
-日本整形外科学会認定運動器リハビリテーション医
-日本スポーツ協会公認スポーツドクター
-日本障がい者スポーツ協会公認障がい者スポーツ医
-日本陸上競技協会公認コーチ</t>
-  </si>
-  <si>
-    <t>臨床経験及び研究に関する実績</t>
-  </si>
-  <si>
-    <t>〈再生医療治療の経験値〉※経験がある場合</t>
-  </si>
-  <si>
-    <t>・脂肪組織由来（幹）細胞を用いた変形性関節症に対する治療：〇症例
-・脂肪組織由来(幹)細胞を用いた慢性疼痛に対する治療：〇症例
-・PRPを用いた筋・腱・靭帯の軟部組織再生療法：〇症例</t>
-  </si>
-  <si>
-    <t>（臨床経験が無い場合：【研修】に関する記載）</t>
-  </si>
-  <si>
-    <t>2025年〇月開催の日本整形外科学会（日本再生医療学会）におけるPRP治療の臨床や治療成績、課題等を題目に上げたセミナーへ参加済み。
-※（京セラ例）2025年8月1日開催の京セラ㈱及びCBC㈱主催のPRP治療の臨床等をテーマに上げたセミナーへ参加済み（座長：東京城南整形外科米川正吾院長、演者：畠山整形外科スポーツクリニック畠山昌久院長他）
-※（マイセル例）〇月〇日日本アンチエイジング医療協会主催の〇〇先生によるPRP治療セミナー
-2025年〇月〇日、PRPキットメーカー〇〇㈱〇〇氏によるPRPキットの利用方法等のデモンストレーション会を開催済み。</t>
-  </si>
-  <si>
-    <t>（臨床経験が無い場合：【指導体制】に関する記載）
-※指導医管理下で数例を指導医と共に実施する体制を求められます（2025年12月記載要請あり）</t>
-  </si>
-  <si>
-    <t>推奨例：PRP治療（幹細胞治療）については、既に治療を実施している当院（又は〇〇病院）の○○医師より2025年〇月に指導を受けております。また、初期の治療は指導を受けながら実施してまいります。
-（代替例：PRP治療を行うに当たり、初期の治療はPRPキットメーカー〇〇㈱〇〇氏による立会いのもと実施して参ります。）</t>
-  </si>
-  <si>
-    <t>（救急医療の知識及び経験の確認） 2025年12月追加確認要請あり</t>
-  </si>
-  <si>
-    <t>記載例）救急医療については、〇〇年（又は〇〇病院勤務時）にACLS・BLS等を受講済み（念のため受講済み証があるかご確認下さい）。
-記載例）救急医療については、〇〇病院に勤めていた際に実務経験があります。</t>
-  </si>
-  <si>
-    <t>（研究・発表実績がある場合のみ）</t>
-  </si>
-  <si>
-    <t>・膝関節病変における多血小板血療法．第○回XXXXXX学会総会・学術大会，XXXX，東京.（学会発表）
-・変形性関節症に対するPRP治療を施行した症例の疼痛改善効果経過観察．○○○○学会誌 XX (X): XX-XX, XXXX（論文）</t>
   </si>
   <si>
     <t>再生医療等の名称</t>
@@ -608,10 +461,6 @@
 分離容器から連通針20Gを外しシーリングキャップを装着。プランジャーを取り外す。
 分離容器をアダプタに投入し、2,000×g・5分間で遠心。PRP層とPPP層に分離。
 ニードルガイド10mL（桃）を分離容器のガスケット上にセットし、回収容器の連通針22Gを通す。回収容器を押し下げてPPP層を回収し、分離容器にPRP層のみを残して調製完了。</t>
-  </si>
-  <si>
-    <t>当院　処置室にて、滅菌汎用注射筒を用いて自家多血小板血漿を患部に投与する。
-投与回数については単回〜複数回投与とする。複数回投与を行う場合には、前回投与後少なくとも1週間以上の間隔を空け、症状経過および有害事象の有無等を確認した上で、患者と相談のうえ追加投与を実施する</t>
   </si>
   <si>
     <t>Mycells PRPキット（スモールスピッツ）</t>
@@ -812,9 +661,6 @@
     <t>03-5542-1597</t>
   </si>
   <si>
-    <t>mail@jscsf.net</t>
-  </si>
-  <si>
     <t>CONCIDE特定認定再生医療等委員会</t>
   </si>
   <si>
@@ -851,13 +697,7 @@
     <t>yauchi240701@gmail.com</t>
   </si>
   <si>
-    <t>医療法人清悠会認定再生医療等委員会</t>
-  </si>
-  <si>
     <t>NB5150007</t>
-  </si>
-  <si>
-    <t>052-891-2527</t>
   </si>
   <si>
     <t>安全未来特定認定再生医療等委員会</t>
@@ -979,10 +819,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>6～30mL</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>60,000円</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -999,10 +835,6 @@
   </si>
   <si>
     <t>PRP投与の場所　※通常：診察室又は処置室</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>再生医療/実施責任者の連絡先（通常院長又は責任者）</t>
     <phoneticPr fontId="1"/>
   </si>
   <si>
@@ -1123,29 +955,6 @@
     <t>診察室又は注射採血室</t>
     <rPh sb="3" eb="4">
       <t>マタ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>吉見 洋平</t>
-    <rPh sb="0" eb="2">
-      <t>ヨシミ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>ヨウヘイ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>大井 知泉</t>
-    <rPh sb="0" eb="2">
-      <t>オオイ</t>
-    </rPh>
-    <rPh sb="3" eb="4">
-      <t>チ</t>
-    </rPh>
-    <rPh sb="4" eb="5">
-      <t>イズミ</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -1242,10 +1051,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>FC1234567</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>大井病院　細胞加工室</t>
     <rPh sb="0" eb="4">
       <t>オオイビョウイン</t>
@@ -1269,33 +1074,160 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>名古屋市名東区高社 1-231 エルパティオ 一社 106</t>
-    <rPh sb="0" eb="4">
-      <t>ナゴヤシ</t>
+    <t>開設者（診療所開設届上）※医療法人の場合（役職も必要）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>他の医療機関</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">救急医療対応(自施設・他施設）
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>※右記の選択肢よりお選びください</t>
+    </r>
+    <rPh sb="4" eb="6">
+      <t>タイオウ</t>
     </rPh>
-    <rPh sb="4" eb="7">
-      <t>メイトウク</t>
+    <rPh sb="17" eb="19">
+      <t>ウキ</t>
+    </rPh>
+    <rPh sb="20" eb="23">
+      <t>センタクシ</t>
+    </rPh>
+    <rPh sb="26" eb="27">
+      <t>エラ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>再生医療を行う医師の役職・氏名</t>
+    <rPh sb="10" eb="12">
+      <t>ヤクショク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>整形外科部長　荒武 佑至</t>
+    <rPh sb="0" eb="6">
+      <t>セイケイゲカブチョウ</t>
+    </rPh>
+    <rPh sb="7" eb="12">
+      <t>オオイビョウイン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>院長　中薗 紀幸</t>
+    <rPh sb="0" eb="2">
+      <t>インチョウ</t>
+    </rPh>
+    <rPh sb="3" eb="8">
+      <t>オオイビョウイン</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>理事長　大井 知泉</t>
+    <rPh sb="0" eb="3">
+      <t>リジチョウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>オオイ</t>
     </rPh>
     <rPh sb="7" eb="8">
-      <t>コウ</t>
+      <t>チ</t>
     </rPh>
     <rPh sb="8" eb="9">
-      <t>シャ</t>
+      <t>イズミ</t>
     </rPh>
-    <rPh sb="23" eb="25">
-      <t>イッシャ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>test@abcmail.com</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t>当院　</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="Yu Gothic"/>
+        <family val="3"/>
+        <charset val="128"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>処置室</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Yu Gothic"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>にて、滅菌汎用注射筒を用いて自家多血小板血漿を患部に投与する。
+投与回数については単回〜複数回投与とする。複数回投与を行う場合には、前回投与後少なくとも1週間以上の間隔を空け、症状経過および有害事象の有無等を確認した上で、患者と相談のうえ追加投与を実施する</t>
+    </r>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>FC2345567</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PRPキットメーカー④（右記タブから選択）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>再生医療⑤（右記タブから選択）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PRPキットメーカー⑤（右記タブから選択）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>PRP製造場所（細胞培養加工施設として届出するお部屋）
+※区画として区切られた部屋（カーテン等は原則不可）
+※通常：処置室が多い</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>mail@jscsf.net</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>医師　吉見 洋平</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>30mL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>再生医療/実施責任者の連絡先（通常院長又は責任者）</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>製造責任者（通常、院長や再生医療をご担当される責任者）</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <fonts count="15">
     <font>
       <sz val="11"/>
@@ -1400,14 +1332,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
-      <name val="Yu Gothic"/>
-      <family val="3"/>
-      <charset val="128"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="14"/>
       <color rgb="FFFF0000"/>
@@ -1416,8 +1340,16 @@
       <charset val="128"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B050"/>
+      <name val="Yu Gothic"/>
+      <family val="3"/>
+      <charset val="128"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1466,8 +1398,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1" tint="0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="7">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -1523,36 +1461,12 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="57">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -1611,12 +1525,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1631,7 +1539,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1661,10 +1569,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1684,7 +1588,6 @@
     <xf numFmtId="0" fontId="9" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1692,6 +1595,23 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment shrinkToFit="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1700,13 +1620,6 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="ハイパーリンク" xfId="1" builtinId="8"/>
@@ -1980,34 +1893,34 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E100"/>
+  <dimension ref="A1:E114"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="5.08203125" style="4" customWidth="1"/>
-    <col min="2" max="2" width="38.83203125" style="11" customWidth="1"/>
-    <col min="3" max="3" width="50.1640625" style="11" customWidth="1"/>
+    <col min="1" max="1" width="5.09765625" style="4" customWidth="1"/>
+    <col min="2" max="2" width="38.796875" style="11" customWidth="1"/>
+    <col min="3" max="3" width="50.19921875" style="11" customWidth="1"/>
     <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="27" customHeight="1">
-      <c r="A1" s="51" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="52"/>
-      <c r="C1" s="52"/>
-    </row>
-    <row r="2" spans="1:4" ht="29.15" customHeight="1">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+    </row>
+    <row r="2" spans="1:4" ht="29.1" customHeight="1">
       <c r="A2" s="6" t="s">
         <v>1</v>
       </c>
@@ -2019,15 +1932,15 @@
       </c>
     </row>
     <row r="3" spans="1:4" ht="24" customHeight="1">
-      <c r="A3" s="53" t="s">
+      <c r="A3" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="54"/>
-      <c r="C3" s="54"/>
-    </row>
-    <row r="4" spans="1:4" ht="24.65" customHeight="1">
+      <c r="B3" s="56"/>
+      <c r="C3" s="56"/>
+    </row>
+    <row r="4" spans="1:4" ht="24.6" customHeight="1">
       <c r="A4" s="13" t="s">
-        <v>276</v>
+        <v>234</v>
       </c>
       <c r="B4" s="12"/>
       <c r="C4" s="8"/>
@@ -2040,7 +1953,7 @@
         <v>5</v>
       </c>
       <c r="C5" s="8" t="s">
-        <v>283</v>
+        <v>241</v>
       </c>
       <c r="D5" t="s">
         <v>6</v>
@@ -2051,10 +1964,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>278</v>
+        <v>236</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>284</v>
+        <v>242</v>
       </c>
       <c r="D6" t="s">
         <v>7</v>
@@ -2066,7 +1979,7 @@
         <v>8</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>285</v>
+        <v>243</v>
       </c>
       <c r="D7" t="s">
         <v>7</v>
@@ -2078,7 +1991,7 @@
         <v>9</v>
       </c>
       <c r="C8" s="8" t="s">
-        <v>286</v>
+        <v>244</v>
       </c>
       <c r="D8" t="s">
         <v>7</v>
@@ -2089,31 +2002,31 @@
         <v>1</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>10</v>
+        <v>268</v>
       </c>
       <c r="C9" s="8" t="s">
-        <v>287</v>
+        <v>245</v>
       </c>
     </row>
     <row r="10" spans="1:4" ht="36">
       <c r="A10" s="2"/>
       <c r="B10" s="1" t="s">
-        <v>277</v>
+        <v>235</v>
       </c>
       <c r="C10" s="8"/>
     </row>
-    <row r="11" spans="1:4" ht="38.5" customHeight="1">
-      <c r="A11" s="40"/>
-      <c r="B11" s="41" t="s">
-        <v>289</v>
-      </c>
-      <c r="C11" s="42" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4" ht="24.65" customHeight="1">
+    <row r="11" spans="1:4" ht="38.549999999999997" customHeight="1">
+      <c r="A11" s="36"/>
+      <c r="B11" s="37" t="s">
+        <v>247</v>
+      </c>
+      <c r="C11" s="38" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="24.6" customHeight="1">
       <c r="A12" s="13" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="B12" s="12"/>
       <c r="C12" s="8"/>
@@ -2123,756 +2036,843 @@
         <v>2</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C13" s="8" t="s">
-        <v>288</v>
+        <v>246</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="2"/>
       <c r="B14" s="1" t="s">
-        <v>265</v>
+        <v>225</v>
       </c>
       <c r="C14" s="8" t="s">
-        <v>291</v>
+        <v>249</v>
       </c>
     </row>
     <row r="15" spans="1:4" ht="18" customHeight="1">
       <c r="A15" s="2"/>
       <c r="B15" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="C15" s="43" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4" ht="24.65" customHeight="1">
+        <v>12</v>
+      </c>
+      <c r="C15" s="39" t="s">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="24.6" customHeight="1">
       <c r="A16" s="13" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B16" s="12"/>
       <c r="C16" s="8"/>
     </row>
-    <row r="17" spans="1:4">
+    <row r="17" spans="1:3">
       <c r="A17" s="2"/>
       <c r="B17" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C17" s="8" t="s">
-        <v>293</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
+        <v>251</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3">
       <c r="A18" s="2"/>
       <c r="B18" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>291</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4" ht="18" customHeight="1">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" ht="18" customHeight="1">
       <c r="A19" s="2"/>
       <c r="B19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C19" s="39" t="s">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" ht="24.6" customHeight="1">
+      <c r="A20" s="13" t="s">
         <v>14</v>
-      </c>
-      <c r="C19" s="43" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" ht="24.65" customHeight="1">
-      <c r="A20" s="13" t="s">
-        <v>16</v>
       </c>
       <c r="B20" s="12"/>
       <c r="C20" s="8"/>
     </row>
-    <row r="21" spans="1:4" ht="75" customHeight="1">
+    <row r="21" spans="1:3" ht="75" customHeight="1">
       <c r="A21" s="2"/>
       <c r="B21" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4" ht="75" customHeight="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" ht="75" customHeight="1">
       <c r="A22" s="2"/>
       <c r="B22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:3" ht="24" customHeight="1">
+      <c r="A23" s="55" t="s">
+        <v>18</v>
+      </c>
+      <c r="B23" s="56"/>
+      <c r="C23" s="56"/>
+    </row>
+    <row r="24" spans="1:3" ht="21.6" customHeight="1">
+      <c r="A24" s="13" t="s">
         <v>19</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4" ht="24" customHeight="1">
-      <c r="A23" s="53" t="s">
-        <v>20</v>
-      </c>
-      <c r="B23" s="54"/>
-      <c r="C23" s="54"/>
-    </row>
-    <row r="24" spans="1:4" ht="21.65" customHeight="1">
-      <c r="A24" s="13" t="s">
-        <v>21</v>
       </c>
       <c r="B24" s="12"/>
       <c r="C24" s="8"/>
     </row>
-    <row r="25" spans="1:4" ht="36">
+    <row r="25" spans="1:3" ht="36">
       <c r="A25" s="2"/>
       <c r="B25" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C25" s="8" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" ht="37.5" customHeight="1">
+      <c r="A26" s="2"/>
+      <c r="B26" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C25" s="8" t="s">
+      <c r="C26" s="8" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="26" spans="1:4" s="48" customFormat="1">
-      <c r="A26" s="44"/>
-      <c r="B26" s="45" t="s">
-        <v>24</v>
-      </c>
-      <c r="C26" s="46" t="s">
-        <v>25</v>
-      </c>
-      <c r="D26" s="47" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="27" spans="1:4" ht="37.5" customHeight="1">
+    <row r="27" spans="1:3">
       <c r="A27" s="2"/>
       <c r="B27" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="C27" s="8" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="28" spans="1:4" s="48" customFormat="1" ht="75" customHeight="1">
-      <c r="A28" s="44"/>
-      <c r="B28" s="45" t="s">
         <v>24</v>
       </c>
-      <c r="C28" s="46" t="s">
-        <v>29</v>
-      </c>
-      <c r="D28" s="47" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="29" spans="1:4">
+      <c r="C27" s="8"/>
+    </row>
+    <row r="28" spans="1:3">
+      <c r="A28" s="2"/>
+      <c r="B28" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C28" s="8"/>
+    </row>
+    <row r="29" spans="1:3">
       <c r="A29" s="2"/>
       <c r="B29" s="1" t="s">
-        <v>30</v>
+        <v>278</v>
       </c>
       <c r="C29" s="8"/>
     </row>
-    <row r="30" spans="1:4">
-      <c r="A30" s="2"/>
-      <c r="B30" s="1" t="s">
-        <v>31</v>
-      </c>
+    <row r="30" spans="1:3" ht="21.6" customHeight="1">
+      <c r="A30" s="13" t="s">
+        <v>257</v>
+      </c>
+      <c r="B30" s="37"/>
       <c r="C30" s="8"/>
     </row>
-    <row r="31" spans="1:4" ht="21.65" customHeight="1">
-      <c r="A31" s="13" t="s">
-        <v>301</v>
-      </c>
-      <c r="B31" s="41"/>
-      <c r="C31" s="8"/>
-    </row>
-    <row r="32" spans="1:4">
+    <row r="31" spans="1:3">
+      <c r="A31" s="2"/>
+      <c r="B31" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C31" s="8" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" ht="36">
       <c r="A32" s="2"/>
-      <c r="B32" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C32" s="8" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="36">
-      <c r="A33" s="2"/>
-      <c r="B33" s="1" t="str">
+      <c r="B32" s="1" t="str">
         <f>B$25&amp;"の治療費の設定（税別）"</f>
         <v>再生医療①（右記タブから選択）の治療費の設定（税別）</v>
       </c>
+      <c r="C32" s="8" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="2"/>
+      <c r="B33" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="C33" s="8" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" s="48" customFormat="1" ht="36">
-      <c r="A34" s="44"/>
-      <c r="B34" s="45" t="str">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="36">
+      <c r="A34" s="2"/>
+      <c r="B34" s="1" t="str">
+        <f>B$26&amp;"の治療費の設定（税別）"</f>
+        <v>再生医療②（右記タブから選択）の治療費の設定（税別）</v>
+      </c>
+      <c r="C34" s="8" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="2"/>
+      <c r="B35" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C35" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5" ht="36">
+      <c r="A36" s="2"/>
+      <c r="B36" s="1" t="str">
         <f>B$27&amp;"の治療費の設定（税別）"</f>
-        <v>再生医療②（右記タブから選択）の治療費の設定（税別）</v>
-      </c>
-      <c r="C34" s="46" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" s="48" customFormat="1" ht="36">
-      <c r="A35" s="44"/>
-      <c r="B35" s="45" t="str">
-        <f>B$29&amp;"の治療費の設定（税別）"</f>
         <v>再生医療③（右記タブから選択）の治療費の設定（税別）</v>
       </c>
-      <c r="C35" s="46" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="2"/>
-      <c r="B36" s="1" t="s">
-        <v>34</v>
-      </c>
       <c r="C36" s="8" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" s="48" customFormat="1" ht="36">
-      <c r="A37" s="44"/>
-      <c r="B37" s="45" t="str">
-        <f>B$25&amp;"の治療費の設定（税別）"</f>
-        <v>再生医療①（右記タブから選択）の治療費の設定（税別）</v>
-      </c>
-      <c r="C37" s="46" t="s">
-        <v>270</v>
+        <v>231</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="2"/>
+      <c r="B37" s="1" t="s">
+        <v>277</v>
+      </c>
+      <c r="C37" s="8" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:5" ht="36">
       <c r="A38" s="2"/>
       <c r="B38" s="1" t="str">
-        <f>B$27&amp;"の治療費の設定（税別）"</f>
-        <v>再生医療②（右記タブから選択）の治療費の設定（税別）</v>
+        <f>B$28&amp;"の治療費の設定（税別）"</f>
+        <v>再生医療④（右記タブから選択）の治療費の設定（税別）</v>
       </c>
       <c r="C38" s="8" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" s="48" customFormat="1" ht="36">
-      <c r="A39" s="44"/>
-      <c r="B39" s="45" t="str">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="2"/>
+      <c r="B39" s="1" t="s">
+        <v>279</v>
+      </c>
+      <c r="C39" s="8" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5" ht="36">
+      <c r="A40" s="2"/>
+      <c r="B40" s="1" t="str">
         <f>B$29&amp;"の治療費の設定（税別）"</f>
-        <v>再生医療③（右記タブから選択）の治療費の設定（税別）</v>
-      </c>
-      <c r="C39" s="46" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="2"/>
-      <c r="B40" s="1" t="s">
+        <v>再生医療⑤（右記タブから選択）の治療費の設定（税別）</v>
+      </c>
+      <c r="C40" s="8" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="2"/>
+      <c r="B41" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C41" s="8" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="13" t="s">
+        <v>33</v>
+      </c>
+      <c r="B42" s="12"/>
+      <c r="C42" s="8"/>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="2"/>
+      <c r="B43" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="C43" s="8"/>
+      <c r="E43" s="25" t="s">
         <v>36</v>
       </c>
-      <c r="C40" s="8" t="s">
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="13" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" s="48" customFormat="1" ht="36">
-      <c r="A41" s="44"/>
-      <c r="B41" s="45" t="str">
-        <f>B$25&amp;"の治療費の設定（税別）"</f>
-        <v>再生医療①（右記タブから選択）の治療費の設定（税別）</v>
-      </c>
-      <c r="C41" s="46" t="s">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" s="48" customFormat="1" ht="36">
-      <c r="A42" s="44"/>
-      <c r="B42" s="45" t="str">
-        <f>B$27&amp;"の治療費の設定（税別）"</f>
-        <v>再生医療②（右記タブから選択）の治療費の設定（税別）</v>
-      </c>
-      <c r="C42" s="46" t="s">
-        <v>271</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" ht="36">
-      <c r="A43" s="2"/>
-      <c r="B43" s="1" t="str">
-        <f>B$29&amp;"の治療費の設定（税別）"</f>
-        <v>再生医療③（右記タブから選択）の治療費の設定（税別）</v>
-      </c>
-      <c r="C43" s="8" t="s">
-        <v>272</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" ht="36">
-      <c r="A44" s="2"/>
-      <c r="B44" s="1" t="s">
-        <v>38</v>
-      </c>
-      <c r="C44" s="8" t="s">
-        <v>269</v>
-      </c>
+      <c r="B44" s="12"/>
+      <c r="C44" s="8"/>
     </row>
     <row r="45" spans="1:5">
-      <c r="A45" s="13" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="12"/>
-      <c r="C45" s="8"/>
-    </row>
-    <row r="46" spans="1:5">
+      <c r="A45" s="2"/>
+      <c r="B45" s="1" t="s">
+        <v>232</v>
+      </c>
+      <c r="C45" s="5" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5" ht="56.25" customHeight="1">
       <c r="A46" s="2"/>
       <c r="B46" s="1" t="s">
-        <v>40</v>
-      </c>
-      <c r="C46" s="8"/>
-      <c r="E46" s="27" t="s">
-        <v>42</v>
+        <v>280</v>
+      </c>
+      <c r="C46" s="21" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="47" spans="1:5">
-      <c r="A47" s="13" t="s">
-        <v>43</v>
-      </c>
-      <c r="B47" s="12"/>
-      <c r="C47" s="8"/>
+      <c r="A47" s="2"/>
+      <c r="B47" s="1" t="s">
+        <v>233</v>
+      </c>
+      <c r="C47" s="21" t="s">
+        <v>255</v>
+      </c>
     </row>
     <row r="48" spans="1:5">
-      <c r="A48" s="2"/>
-      <c r="B48" s="1" t="s">
+      <c r="A48" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="B48" s="12"/>
+      <c r="C48" s="8"/>
+    </row>
+    <row r="49" spans="1:3">
+      <c r="A49" s="19"/>
+      <c r="B49" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C49" s="46" t="s">
+        <v>272</v>
+      </c>
+    </row>
+    <row r="50" spans="1:3">
+      <c r="A50" s="19"/>
+      <c r="B50" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C50" s="47" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="51" spans="1:3">
+      <c r="A51" s="19"/>
+      <c r="B51" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C51" s="47" t="s">
         <v>273</v>
       </c>
-      <c r="C48" s="5" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="56.25" customHeight="1">
-      <c r="A49" s="2"/>
-      <c r="B49" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="C49" s="23" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3">
-      <c r="A50" s="2"/>
-      <c r="B50" s="1" t="s">
-        <v>274</v>
-      </c>
-      <c r="C50" s="23" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3">
-      <c r="A51" s="13" t="s">
-        <v>45</v>
-      </c>
-      <c r="B51" s="12"/>
-      <c r="C51" s="8"/>
     </row>
     <row r="52" spans="1:3">
       <c r="A52" s="19"/>
-      <c r="B52" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C52" s="5" t="s">
-        <v>288</v>
+      <c r="B52" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C52" s="47" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="53" spans="1:3">
       <c r="A53" s="19"/>
-      <c r="B53" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C53" s="23" t="s">
-        <v>299</v>
-      </c>
+      <c r="B53" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C53" s="47"/>
     </row>
     <row r="54" spans="1:3">
       <c r="A54" s="19"/>
-      <c r="B54" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="C54" s="23" t="s">
-        <v>290</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="36">
+      <c r="B54" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C54" s="47"/>
+    </row>
+    <row r="55" spans="1:3">
       <c r="A55" s="19"/>
-      <c r="B55" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="C55" s="23" t="s">
-        <v>298</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="36">
-      <c r="A56" s="2"/>
-      <c r="B56" s="1" t="s">
-        <v>48</v>
-      </c>
-      <c r="C56" s="23" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="30" customHeight="1">
-      <c r="A57" s="2"/>
-      <c r="B57" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="C57" s="23" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="58" spans="1:3" ht="198" customHeight="1">
-      <c r="A58" s="2"/>
-      <c r="B58" s="1" t="s">
-        <v>266</v>
-      </c>
-      <c r="C58" s="23" t="s">
-        <v>300</v>
-      </c>
-    </row>
-    <row r="59" spans="1:3" s="48" customFormat="1">
-      <c r="A59" s="49" t="s">
-        <v>50</v>
-      </c>
-      <c r="B59" s="45"/>
-      <c r="C59" s="46"/>
-    </row>
-    <row r="60" spans="1:3" s="48" customFormat="1" ht="57.9" customHeight="1">
-      <c r="A60" s="44"/>
-      <c r="B60" s="45" t="s">
-        <v>51</v>
-      </c>
-      <c r="C60" s="45" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="61" spans="1:3" s="48" customFormat="1" ht="47.75" customHeight="1">
-      <c r="A61" s="44"/>
-      <c r="B61" s="45" t="s">
-        <v>268</v>
-      </c>
-      <c r="C61" s="45"/>
+      <c r="B55" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C55" s="47"/>
+    </row>
+    <row r="56" spans="1:3">
+      <c r="A56" s="19"/>
+      <c r="B56" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C56" s="47"/>
+    </row>
+    <row r="57" spans="1:3">
+      <c r="A57" s="19"/>
+      <c r="B57" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C57" s="47"/>
+    </row>
+    <row r="58" spans="1:3">
+      <c r="A58" s="19"/>
+      <c r="B58" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C58" s="47"/>
+    </row>
+    <row r="59" spans="1:3">
+      <c r="A59" s="19"/>
+      <c r="B59" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C59" s="47"/>
+    </row>
+    <row r="60" spans="1:3">
+      <c r="A60" s="19"/>
+      <c r="B60" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C60" s="47"/>
+    </row>
+    <row r="61" spans="1:3">
+      <c r="A61" s="19"/>
+      <c r="B61" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C61" s="47"/>
     </row>
     <row r="62" spans="1:3">
-      <c r="A62" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="B62" s="12"/>
-      <c r="C62" s="8"/>
+      <c r="A62" s="19"/>
+      <c r="B62" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C62" s="47"/>
     </row>
     <row r="63" spans="1:3">
-      <c r="A63" s="2"/>
-      <c r="B63" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="C63" s="8"/>
-    </row>
-    <row r="64" spans="1:3" ht="36">
-      <c r="A64" s="2"/>
-      <c r="B64" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="C64" s="8" t="s">
-        <v>302</v>
-      </c>
+      <c r="A63" s="19"/>
+      <c r="B63" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C63" s="47"/>
+    </row>
+    <row r="64" spans="1:3">
+      <c r="A64" s="19"/>
+      <c r="B64" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C64" s="47"/>
     </row>
     <row r="65" spans="1:3">
-      <c r="A65" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="B65" s="12"/>
-      <c r="C65" s="18"/>
-    </row>
-    <row r="66" spans="1:3" ht="150" customHeight="1">
-      <c r="A66" s="2"/>
-      <c r="B66" s="1" t="s">
-        <v>58</v>
-      </c>
-      <c r="C66" s="5" t="s">
-        <v>303</v>
-      </c>
-    </row>
-    <row r="67" spans="1:3" ht="198.9" customHeight="1">
-      <c r="A67" s="2"/>
-      <c r="B67" s="1" t="s">
-        <v>267</v>
-      </c>
-      <c r="C67" s="5" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="68" spans="1:3" ht="24" customHeight="1">
-      <c r="A68" s="53" t="s">
-        <v>59</v>
-      </c>
-      <c r="B68" s="54"/>
-      <c r="C68" s="54"/>
-    </row>
-    <row r="69" spans="1:3">
-      <c r="A69" s="7"/>
-      <c r="B69" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="C69" s="8"/>
-    </row>
-    <row r="70" spans="1:3" ht="36">
+      <c r="A65" s="19"/>
+      <c r="B65" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C65" s="47"/>
+    </row>
+    <row r="66" spans="1:3">
+      <c r="A66" s="19"/>
+      <c r="B66" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C66" s="47"/>
+    </row>
+    <row r="67" spans="1:3">
+      <c r="A67" s="19"/>
+      <c r="B67" s="37" t="s">
+        <v>271</v>
+      </c>
+      <c r="C67" s="47"/>
+    </row>
+    <row r="68" spans="1:3" ht="36">
+      <c r="A68" s="19"/>
+      <c r="B68" s="37" t="s">
+        <v>39</v>
+      </c>
+      <c r="C68" s="47"/>
+    </row>
+    <row r="69" spans="1:3" ht="36">
+      <c r="A69" s="2"/>
+      <c r="B69" s="1" t="s">
+        <v>285</v>
+      </c>
+      <c r="C69" s="21" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="70" spans="1:3" ht="30" customHeight="1">
       <c r="A70" s="2"/>
-      <c r="B70" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C70" s="9"/>
-    </row>
-    <row r="71" spans="1:3" ht="36">
+      <c r="B70" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="C70" s="21" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="71" spans="1:3" ht="198" customHeight="1">
       <c r="A71" s="2"/>
       <c r="B71" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="C71" s="5" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="72" spans="1:3" ht="56.25" customHeight="1">
-      <c r="A72" s="2"/>
-      <c r="B72" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="C72" s="5" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="73" spans="1:3">
-      <c r="A73" s="2"/>
-      <c r="B73" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="C73" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="74" spans="1:3" ht="37.5" customHeight="1">
-      <c r="A74" s="2"/>
-      <c r="B74" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C74" s="5" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="75" spans="1:3" ht="24" customHeight="1">
-      <c r="A75" s="53" t="s">
-        <v>69</v>
-      </c>
-      <c r="B75" s="54"/>
-      <c r="C75" s="54"/>
-    </row>
-    <row r="76" spans="1:3" ht="36">
+        <v>226</v>
+      </c>
+      <c r="C71" s="21" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="72" spans="1:3" s="43" customFormat="1">
+      <c r="A72" s="44" t="s">
+        <v>41</v>
+      </c>
+      <c r="B72" s="41"/>
+      <c r="C72" s="42"/>
+    </row>
+    <row r="73" spans="1:3" s="43" customFormat="1" ht="57.9" customHeight="1">
+      <c r="A73" s="40"/>
+      <c r="B73" s="41" t="s">
+        <v>42</v>
+      </c>
+      <c r="C73" s="41" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="74" spans="1:3" s="43" customFormat="1" ht="47.7" customHeight="1">
+      <c r="A74" s="40"/>
+      <c r="B74" s="41" t="s">
+        <v>228</v>
+      </c>
+      <c r="C74" s="41"/>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="13" t="s">
+        <v>44</v>
+      </c>
+      <c r="B75" s="12"/>
+      <c r="C75" s="8"/>
+    </row>
+    <row r="76" spans="1:3">
       <c r="A76" s="2"/>
-      <c r="B76" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="C76" s="5" t="s">
-        <v>71</v>
-      </c>
+      <c r="B76" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="C76" s="8"/>
     </row>
     <row r="77" spans="1:3" ht="36">
       <c r="A77" s="2"/>
-      <c r="B77" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="C77" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="78" spans="1:3" ht="36">
-      <c r="A78" s="2"/>
-      <c r="B78" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="C78" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="79" spans="1:3" ht="56.25" hidden="1" customHeight="1">
-      <c r="A79" s="2">
-        <v>11</v>
-      </c>
+      <c r="B77" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="C77" s="8" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="13" t="s">
+        <v>48</v>
+      </c>
+      <c r="B78" s="12"/>
+      <c r="C78" s="18"/>
+    </row>
+    <row r="79" spans="1:3" ht="150" customHeight="1">
+      <c r="A79" s="2"/>
       <c r="B79" s="1" t="s">
-        <v>74</v>
+        <v>49</v>
       </c>
       <c r="C79" s="5" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="80" spans="1:3" ht="37.5" hidden="1" customHeight="1">
-      <c r="A80" s="2">
-        <v>12</v>
-      </c>
+        <v>259</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3" ht="37.5" customHeight="1">
+      <c r="A80" s="2"/>
       <c r="B80" s="1" t="s">
-        <v>76</v>
+        <v>270</v>
       </c>
       <c r="C80" s="5" t="s">
-        <v>77</v>
+        <v>269</v>
+      </c>
+    </row>
+    <row r="81" spans="1:3" ht="198.9" customHeight="1">
+      <c r="A81" s="2"/>
+      <c r="B81" s="1" t="s">
+        <v>227</v>
+      </c>
+      <c r="C81" s="5" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="82" spans="1:3" ht="24" customHeight="1">
-      <c r="A82" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="B82" s="29"/>
-      <c r="C82" s="22"/>
+      <c r="A82" s="55" t="s">
+        <v>50</v>
+      </c>
+      <c r="B82" s="56"/>
+      <c r="C82" s="56"/>
     </row>
     <row r="83" spans="1:3">
-      <c r="A83" s="24" t="s">
-        <v>79</v>
-      </c>
-      <c r="B83" s="25"/>
+      <c r="A83" s="7"/>
+      <c r="B83" s="3" t="s">
+        <v>51</v>
+      </c>
       <c r="C83" s="8"/>
     </row>
-    <row r="84" spans="1:3">
+    <row r="84" spans="1:3" ht="36">
       <c r="A84" s="2"/>
-      <c r="B84" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C84" s="5" t="s">
-        <v>306</v>
-      </c>
-    </row>
-    <row r="85" spans="1:3">
+      <c r="B84" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="C84" s="9"/>
+    </row>
+    <row r="85" spans="1:3" ht="36">
       <c r="A85" s="2"/>
       <c r="B85" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C85" s="23" t="s">
-        <v>307</v>
-      </c>
-    </row>
-    <row r="86" spans="1:3">
+        <v>53</v>
+      </c>
+      <c r="C85" s="5" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="86" spans="1:3" ht="56.25" customHeight="1">
       <c r="A86" s="2"/>
       <c r="B86" s="1" t="s">
-        <v>279</v>
-      </c>
-      <c r="C86" s="23" t="s">
-        <v>308</v>
+        <v>55</v>
+      </c>
+      <c r="C86" s="5" t="s">
+        <v>56</v>
       </c>
     </row>
     <row r="87" spans="1:3">
-      <c r="A87" s="24" t="s">
-        <v>82</v>
-      </c>
-      <c r="B87" s="25"/>
-      <c r="C87" s="8"/>
-    </row>
-    <row r="88" spans="1:3">
+      <c r="A87" s="2"/>
+      <c r="B87" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C87" s="5" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="88" spans="1:3" ht="84" customHeight="1">
       <c r="A88" s="2"/>
       <c r="B88" s="1" t="s">
-        <v>83</v>
+        <v>59</v>
       </c>
       <c r="C88" s="5" t="s">
-        <v>309</v>
-      </c>
-    </row>
-    <row r="89" spans="1:3">
-      <c r="A89" s="2"/>
-      <c r="B89" s="1" t="s">
-        <v>84</v>
-      </c>
-      <c r="C89" s="5" t="s">
-        <v>310</v>
-      </c>
-    </row>
-    <row r="90" spans="1:3">
-      <c r="A90" s="24" t="s">
-        <v>85</v>
-      </c>
-      <c r="B90" s="25"/>
-      <c r="C90" s="8"/>
-    </row>
-    <row r="91" spans="1:3">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="89" spans="1:3" ht="24" customHeight="1">
+      <c r="A89" s="55" t="s">
+        <v>60</v>
+      </c>
+      <c r="B89" s="56"/>
+      <c r="C89" s="56"/>
+    </row>
+    <row r="90" spans="1:3" ht="36">
+      <c r="A90" s="2"/>
+      <c r="B90" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="C90" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="91" spans="1:3" ht="36">
       <c r="A91" s="2"/>
-      <c r="B91" s="1" t="s">
-        <v>86</v>
+      <c r="B91" s="3" t="s">
+        <v>63</v>
       </c>
       <c r="C91" s="5" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="92" spans="1:3">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="92" spans="1:3" ht="36">
       <c r="A92" s="2"/>
-      <c r="B92" s="1" t="s">
-        <v>280</v>
-      </c>
-      <c r="C92" s="1" t="s">
-        <v>229</v>
-      </c>
-    </row>
-    <row r="93" spans="1:3">
-      <c r="A93" s="2"/>
-      <c r="B93" s="30" t="s">
-        <v>87</v>
-      </c>
-      <c r="C93" s="30" t="s">
-        <v>213</v>
-      </c>
-    </row>
-    <row r="94" spans="1:3">
-      <c r="A94" s="2"/>
-      <c r="B94" s="30" t="s">
-        <v>88</v>
-      </c>
-      <c r="C94" s="30" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="95" spans="1:3">
-      <c r="A95" s="2"/>
-      <c r="B95" s="30" t="s">
-        <v>89</v>
-      </c>
-      <c r="C95" s="50" t="s">
-        <v>230</v>
-      </c>
-    </row>
-    <row r="96" spans="1:3" ht="22.5" customHeight="1">
-      <c r="A96" s="2"/>
-      <c r="B96" s="30" t="s">
-        <v>90</v>
-      </c>
-      <c r="C96" s="43" t="s">
-        <v>314</v>
-      </c>
-    </row>
-    <row r="97" spans="1:3" ht="24.65" customHeight="1">
-      <c r="A97" s="24" t="s">
-        <v>16</v>
-      </c>
-      <c r="B97" s="25"/>
+      <c r="B92" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C92" s="5" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="93" spans="1:3" ht="56.25" hidden="1" customHeight="1">
+      <c r="A93" s="2">
+        <v>11</v>
+      </c>
+      <c r="B93" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C93" s="5" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="94" spans="1:3" ht="37.5" hidden="1" customHeight="1">
+      <c r="A94" s="2">
+        <v>12</v>
+      </c>
+      <c r="B94" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="C94" s="5" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="96" spans="1:3" ht="24" customHeight="1">
+      <c r="A96" s="26" t="s">
+        <v>69</v>
+      </c>
+      <c r="B96" s="27"/>
+      <c r="C96" s="20"/>
+    </row>
+    <row r="97" spans="1:3">
+      <c r="A97" s="22" t="s">
+        <v>70</v>
+      </c>
+      <c r="B97" s="23"/>
       <c r="C97" s="8"/>
     </row>
-    <row r="98" spans="1:3" ht="75" customHeight="1">
+    <row r="98" spans="1:3">
       <c r="A98" s="2"/>
       <c r="B98" s="1" t="s">
-        <v>91</v>
+        <v>71</v>
       </c>
       <c r="C98" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="99" spans="1:3" ht="75" customHeight="1">
+        <v>262</v>
+      </c>
+    </row>
+    <row r="99" spans="1:3">
       <c r="A99" s="2"/>
       <c r="B99" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="C99" s="5" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="100" spans="1:3" ht="75" customHeight="1">
+        <v>72</v>
+      </c>
+      <c r="C99" s="21" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="100" spans="1:3">
       <c r="A100" s="2"/>
       <c r="B100" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C100" s="5" t="s">
-        <v>18</v>
+        <v>237</v>
+      </c>
+      <c r="C100" s="21" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="101" spans="1:3">
+      <c r="A101" s="22" t="s">
+        <v>73</v>
+      </c>
+      <c r="B101" s="23"/>
+      <c r="C101" s="8"/>
+    </row>
+    <row r="102" spans="1:3">
+      <c r="A102" s="2"/>
+      <c r="B102" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C102" s="5" t="s">
+        <v>264</v>
+      </c>
+    </row>
+    <row r="103" spans="1:3">
+      <c r="A103" s="2"/>
+      <c r="B103" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C103" s="5" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="104" spans="1:3">
+      <c r="A104" s="22" t="s">
+        <v>76</v>
+      </c>
+      <c r="B104" s="23"/>
+      <c r="C104" s="8"/>
+    </row>
+    <row r="105" spans="1:3">
+      <c r="A105" s="2"/>
+      <c r="B105" s="1" t="s">
+        <v>77</v>
+      </c>
+      <c r="C105" s="5" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="106" spans="1:3">
+      <c r="A106" s="2"/>
+      <c r="B106" s="1" t="s">
+        <v>238</v>
+      </c>
+      <c r="C106" s="1" t="str">
+        <f>VLOOKUP($C$105,審査委員会!$A$2:$F$11,2,FALSE)</f>
+        <v>NB3160004</v>
+      </c>
+    </row>
+    <row r="107" spans="1:3">
+      <c r="A107" s="2"/>
+      <c r="B107" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="C107" s="28" t="str">
+        <f>VLOOKUP($C$105,審査委員会!$A$2:$F$11,3,FALSE)</f>
+        <v>一般社団法人日本保健情報コンソシウム</v>
+      </c>
+    </row>
+    <row r="108" spans="1:3">
+      <c r="A108" s="2"/>
+      <c r="B108" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="C108" s="28" t="str">
+        <f>VLOOKUP($C$105,審査委員会!$A$2:$F$11,4,FALSE)</f>
+        <v>東京都千代田区二番町11-3 相互二番町ビルディング別館7階</v>
+      </c>
+    </row>
+    <row r="109" spans="1:3">
+      <c r="A109" s="2"/>
+      <c r="B109" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="C109" s="45" t="str">
+        <f>VLOOKUP($C$105,審査委員会!$A$2:$F$11,5,FALSE)</f>
+        <v>03-5772-7584</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" ht="32.549999999999997" customHeight="1">
+      <c r="A110" s="2"/>
+      <c r="B110" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="C110" s="45">
+        <f>VLOOKUP($C$105,審査委員会!$A$2:$F$11,6,FALSE)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" ht="24.6" customHeight="1">
+      <c r="A111" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="B111" s="23"/>
+      <c r="C111" s="8"/>
+    </row>
+    <row r="112" spans="1:3" ht="75" customHeight="1">
+      <c r="A112" s="2"/>
+      <c r="B112" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="C112" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" ht="75" customHeight="1">
+      <c r="A113" s="2"/>
+      <c r="B113" s="1" t="s">
+        <v>83</v>
+      </c>
+      <c r="C113" s="5" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" ht="75" customHeight="1">
+      <c r="A114" s="2"/>
+      <c r="B114" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C114" s="5" t="s">
+        <v>16</v>
       </c>
     </row>
   </sheetData>
@@ -2880,175 +2880,404 @@
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A23:C23"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A68:C68"/>
-    <mergeCell ref="A75:C75"/>
+    <mergeCell ref="A82:C82"/>
+    <mergeCell ref="A89:C89"/>
   </mergeCells>
   <phoneticPr fontId="1"/>
+  <dataValidations count="1">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C80">
+      <formula1>"自施設,他の医療機関"</formula1>
+    </dataValidation>
+  </dataValidations>
   <hyperlinks>
-    <hyperlink ref="C15" r:id="rId1" xr:uid="{00000000-0004-0000-0000-000000000000}"/>
-    <hyperlink ref="C19" r:id="rId2" xr:uid="{00000000-0004-0000-0000-000001000000}"/>
-    <hyperlink ref="C96" r:id="rId3" xr:uid="{0C4CE975-F560-486B-943A-1D7BAFB0A912}"/>
+    <hyperlink ref="C15" r:id="rId1"/>
+    <hyperlink ref="C19" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.15748031496062989" bottom="0" header="0.31496062992125978" footer="0.31496062992125978"/>
-  <pageSetup paperSize="9" scale="97" fitToHeight="0" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" scale="97" fitToHeight="0" orientation="portrait" r:id="rId3"/>
   <headerFooter>
     <oddFooter>&amp;R&amp;P</oddFooter>
   </headerFooter>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>審査委員会!$A$2:$A$11</xm:f>
+          </x14:formula1>
+          <xm:sqref>C105</xm:sqref>
+        </x14:dataValidation>
+      </x14:dataValidations>
+    </ext>
+  </extLst>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:B20"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:D26"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="21" style="14" customWidth="1"/>
-    <col min="2" max="2" width="83.58203125" style="21" customWidth="1"/>
+    <col min="1" max="1" width="10.69921875" style="14" customWidth="1"/>
+    <col min="2" max="2" width="9.19921875" style="14" customWidth="1"/>
+    <col min="3" max="3" width="62.8984375" style="15" customWidth="1"/>
+    <col min="4" max="4" width="35.09765625" style="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="55.4" customHeight="1">
-      <c r="A1" s="57" t="s">
+    <row r="1" spans="1:4">
+      <c r="A1" s="14" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" s="14" t="s">
+        <v>86</v>
+      </c>
+      <c r="B3" s="14" t="s">
+        <v>87</v>
+      </c>
+      <c r="C3" s="15" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="15" t="s">
+        <v>23</v>
+      </c>
+      <c r="D4" s="16" t="str">
+        <f t="shared" ref="D4:D26" si="0">A4&amp;"/"&amp;B4&amp;"/"&amp;C4</f>
+        <v>3種PRP/整形外科/四肢の筋・腱・靱帯及びその付着部の傷害を対象とした自家多血小板血漿（PRP）注入療法</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B5" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>2種PRP/整形外科/自家多血小板血漿（PRP）を用いた関節内組織損傷に対する治療</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B6" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C6" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="D6" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>3種PRP/美容/皮膚/PRP(多血小板血漿)を用いた皮膚の再生を目的とした再生医療</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" s="14" t="s">
+        <v>89</v>
+      </c>
+      <c r="B7" s="14" t="s">
         <v>94</v>
       </c>
-      <c r="B1" s="52"/>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="19" t="s">
-        <v>12</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="C7" s="15" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="19"/>
-      <c r="B3" s="5" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="19" t="s">
+      <c r="D7" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>3種PRP/AGA/PRP(多血小板血漿)を用いた育毛を目的とした再生医療</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B8" s="14" t="s">
         <v>96</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="C8" s="15" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="19" t="s">
+      <c r="D8" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>2種PRP/不妊治療/子宮内膜に対する自家多血小板血漿（自家PRP）を用いた反復性着床不全を対象とした不妊治療</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" s="14" t="s">
+        <v>91</v>
+      </c>
+      <c r="B9" s="14" t="s">
+        <v>96</v>
+      </c>
+      <c r="C9" s="15" t="s">
         <v>98</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="D9" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>2種PRP/不妊治療/卵巣に対する自家多血小板血漿（自家PRP）を用いた不妊治療</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" s="14" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="19" t="s">
+      <c r="B10" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C10" s="15" t="s">
         <v>100</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="D10" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>2種繊維芽/美容/皮膚/自家培養真皮線維芽細胞を用いた皮膚再生治療</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" s="14" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" ht="282.64999999999998" customHeight="1">
-      <c r="A7" s="1" t="s">
+      <c r="B11" s="14" t="s">
+        <v>92</v>
+      </c>
+      <c r="C11" s="15" t="s">
         <v>102</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="D11" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>2種幹細胞/美容/皮膚/自己脂肪由来幹細胞を用いた皮膚の再生を目的とした再生医療</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" s="14" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="19" t="s">
+      <c r="B12" s="14" t="s">
         <v>104</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="C12" s="15" t="s">
         <v>105</v>
       </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="19" t="s">
+      <c r="D12" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>3種免疫療法/免疫/美容/がんの治療と予防を目的としたNK細胞を用いたアンチエイジング療法</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B13" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C13" s="15" t="s">
         <v>106</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="D13" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>2種幹細胞/整形外科/自己脂肪組織由来培養間葉系幹細胞を用いた関節系疾患に対する治療（局所投与）</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B14" s="14" t="s">
+        <v>90</v>
+      </c>
+      <c r="C14" s="15" t="s">
         <v>107</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" ht="93.75" customHeight="1">
-      <c r="A10" s="19" t="s">
+      <c r="D14" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>2種幹細胞/整形外科/変形性関節症に対する自己滑膜由来培養間葉系幹細胞の関節内投与療法</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4">
+      <c r="A15" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B15" s="14" t="s">
         <v>108</v>
       </c>
-      <c r="B10" s="5" t="s">
+      <c r="C15" s="15" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="55" t="s">
+      <c r="D15" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>2種幹細胞/全般/動脈硬化関連血管障害リスクの低減を目的とした自己脂肪組織由来幹細胞治療</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4">
+      <c r="A16" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" s="14" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" s="15" t="s">
         <v>110</v>
       </c>
-      <c r="B11" s="20" t="s">
+      <c r="D16" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>2種幹細胞/全般/自己脂肪由来幹細胞を用いた慢性疼痛治療</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4">
+      <c r="A17" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B17" s="14" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" ht="56.25" customHeight="1">
-      <c r="A12" s="56"/>
-      <c r="B12" s="5" t="s">
+      <c r="C17" s="15" t="s">
         <v>112</v>
       </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="56"/>
-      <c r="B13" s="20" t="s">
+      <c r="D17" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>2種幹細胞/脳外科/自己脂肪由来幹細胞を用いた脳血管障害治療</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B18" s="14" t="s">
         <v>113</v>
       </c>
-    </row>
-    <row r="14" spans="1:2" ht="150" customHeight="1">
-      <c r="A14" s="56"/>
-      <c r="B14" s="5" t="s">
+      <c r="C18" s="15" t="s">
         <v>114</v>
       </c>
-    </row>
-    <row r="15" spans="1:2" ht="36" customHeight="1">
-      <c r="A15" s="56"/>
-      <c r="B15" s="20" t="s">
+      <c r="D18" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>2種幹細胞/婦人科/自己脂肪由来幹細胞を用いたフレイル治療</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B19" s="14" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19" s="15" t="s">
         <v>115</v>
       </c>
-    </row>
-    <row r="16" spans="1:2" ht="93.75" customHeight="1">
-      <c r="A16" s="56"/>
-      <c r="B16" s="5" t="s">
+      <c r="D19" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>2種幹細胞/婦人科/自己脂肪由来幹細胞を用いた更年期障害治療</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B20" s="14" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="56"/>
-      <c r="B17" s="20" t="s">
+      <c r="C20" s="15" t="s">
         <v>117</v>
       </c>
-    </row>
-    <row r="18" spans="1:2" ht="56.25" customHeight="1">
-      <c r="A18" s="56"/>
-      <c r="B18" s="22" t="s">
+      <c r="D20" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>2種幹細胞/内科/自己脂肪由来幹細胞を用いた肝障害治療</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B21" s="14" t="s">
+        <v>116</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>118</v>
       </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="56"/>
-      <c r="B19" s="20" t="s">
+      <c r="D21" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>2種幹細胞/内科/自己脂肪由来幹細胞を用いた糖尿病治療</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B22" s="14" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" s="15" t="s">
         <v>119</v>
       </c>
-    </row>
-    <row r="20" spans="1:2" ht="75" customHeight="1">
-      <c r="A20" s="56"/>
-      <c r="B20" s="5" t="s">
+      <c r="D22" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>2種幹細胞/AGA/自己脂肪由来幹細胞を用いた毛髪組織の治療（局所投与）</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" s="14" t="s">
         <v>120</v>
       </c>
+      <c r="C23" s="15" t="s">
+        <v>121</v>
+      </c>
+      <c r="D23" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>2種幹細胞/泌尿器科/自己脂肪由来幹細胞を用いたED（勃起不全）治療（局所投与）</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" ht="37.5" customHeight="1">
+      <c r="A24" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B24" s="14" t="s">
+        <v>122</v>
+      </c>
+      <c r="C24" s="17" t="s">
+        <v>123</v>
+      </c>
+      <c r="D24" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>2種幹細胞/皮膚/アトピー性皮膚炎患者の主症状に対する自己脂肪由来間葉系
+幹細胞による治療</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="14" t="s">
+        <v>101</v>
+      </c>
+      <c r="B25" s="14" t="s">
+        <v>124</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>125</v>
+      </c>
+      <c r="D25" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v xml:space="preserve">2種幹細胞/免疫治療/自己脂肪（組織）由来間葉系幹細胞を用いた自己免疫疾患の治療 </v>
+      </c>
+    </row>
+    <row r="26" spans="1:4">
+      <c r="D26" s="16" t="str">
+        <f t="shared" si="0"/>
+        <v>//</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A11:A20"/>
-    <mergeCell ref="A1:B1"/>
-  </mergeCells>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
@@ -3056,367 +3285,219 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:D26"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <sheetPr>
+    <tabColor theme="7" tint="0.59999389629810485"/>
+  </sheetPr>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="10.6640625" style="14" customWidth="1"/>
-    <col min="2" max="2" width="9.1640625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="62.9140625" style="15" customWidth="1"/>
-    <col min="4" max="4" width="35.08203125" style="14" customWidth="1"/>
+    <col min="1" max="1" width="43.19921875" style="14" customWidth="1"/>
+    <col min="2" max="2" width="22.3984375" style="14" customWidth="1"/>
+    <col min="3" max="3" width="55.5" style="14" customWidth="1"/>
+    <col min="4" max="4" width="60.09765625" style="14" customWidth="1"/>
+    <col min="5" max="5" width="47.3984375" style="51" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="14" t="s">
-        <v>121</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="14" t="s">
-        <v>122</v>
-      </c>
-      <c r="B3" s="14" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="15" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="B4" s="14" t="s">
+    <row r="1" spans="1:5">
+      <c r="E1" s="48" t="s">
         <v>126</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D4" s="16" t="str">
-        <f t="shared" ref="D4:D26" si="0">A4&amp;"/"&amp;B4&amp;"/"&amp;C4</f>
-        <v>3種PRP/整形外科/四肢の筋・腱・靱帯及びその付着部の傷害を対象とした自家多血小板血漿（PRP）注入療法</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="14" t="s">
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="B5" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D5" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>2種PRP/整形外科/自家多血小板血漿（PRP）を用いた関節内組織損傷に対する治療</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="B6" s="14" t="s">
+      <c r="B2" s="19" t="s">
         <v>128</v>
       </c>
-      <c r="C6" s="15" t="s">
+      <c r="C2" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="D6" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>3種PRP/美容/皮膚/PRP(多血小板血漿)を用いた皮膚の再生を目的とした再生医療</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="14" t="s">
-        <v>125</v>
-      </c>
-      <c r="B7" s="14" t="s">
+      <c r="D2" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="E2" s="49" t="s">
         <v>131</v>
       </c>
-      <c r="D7" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>3種PRP/AGA/PRP(多血小板血漿)を用いた育毛を目的とした再生医療</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="B8" s="14" t="s">
+    </row>
+    <row r="3" spans="1:5" ht="332.55" customHeight="1">
+      <c r="A3" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="B3" s="19">
+        <v>20</v>
+      </c>
+      <c r="C3" s="1" t="s">
         <v>132</v>
       </c>
-      <c r="C8" s="15" t="s">
+      <c r="D3" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="D8" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>2種PRP/不妊治療/子宮内膜に対する自家多血小板血漿（自家PRP）を用いた反復性着床不全を対象とした不妊治療</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="14" t="s">
-        <v>127</v>
-      </c>
-      <c r="B9" s="14" t="s">
-        <v>132</v>
-      </c>
-      <c r="C9" s="15" t="s">
+      <c r="E3" s="50" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="187.5" customHeight="1">
+      <c r="A4" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="D9" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>2種PRP/不妊治療/卵巣に対する自家多血小板血漿（自家PRP）を用いた不妊治療</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="14" t="s">
+      <c r="B4" s="19">
+        <v>11</v>
+      </c>
+      <c r="C4" s="1" t="s">
         <v>135</v>
       </c>
-      <c r="B10" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C10" s="15" t="s">
+      <c r="D4" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="D10" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>2種繊維芽/美容/皮膚/自家培養真皮線維芽細胞を用いた皮膚再生治療</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="14" t="s">
+      <c r="E4" s="50" t="s">
         <v>137</v>
       </c>
-      <c r="B11" s="14" t="s">
-        <v>128</v>
-      </c>
-      <c r="C11" s="15" t="s">
+    </row>
+    <row r="5" spans="1:5" ht="187.5" customHeight="1">
+      <c r="A5" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D11" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>2種幹細胞/美容/皮膚/自己脂肪由来幹細胞を用いた皮膚の再生を目的とした再生医療</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="14" t="s">
+      <c r="B5" s="19">
+        <v>22</v>
+      </c>
+      <c r="C5" s="1" t="s">
         <v>139</v>
       </c>
-      <c r="B12" s="14" t="s">
+      <c r="D5" s="1" t="s">
+        <v>136</v>
+      </c>
+      <c r="E5" s="50" t="s">
         <v>140</v>
       </c>
-      <c r="C12" s="15" t="s">
+    </row>
+    <row r="6" spans="1:5" ht="206.25" customHeight="1">
+      <c r="A6" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="D12" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>3種免疫療法/免疫/美容/がんの治療と予防を目的としたNK細胞を用いたアンチエイジング療法</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B13" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C13" s="15" t="s">
+      <c r="B6" s="19">
+        <v>15</v>
+      </c>
+      <c r="C6" s="1" t="s">
         <v>142</v>
       </c>
-      <c r="D13" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>2種幹細胞/整形外科/自己脂肪組織由来培養間葉系幹細胞を用いた関節系疾患に対する治療（局所投与）</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B14" s="14" t="s">
-        <v>126</v>
-      </c>
-      <c r="C14" s="15" t="s">
+      <c r="D6" s="1" t="s">
         <v>143</v>
       </c>
-      <c r="D14" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>2種幹細胞/整形外科/変形性関節症に対する自己滑膜由来培養間葉系幹細胞の関節内投与療法</v>
-      </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B15" s="14" t="s">
+      <c r="E6" s="50" t="s">
         <v>144</v>
       </c>
-      <c r="C15" s="15" t="s">
+    </row>
+    <row r="7" spans="1:5" ht="206.25" customHeight="1">
+      <c r="A7" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="D15" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>2種幹細胞/全般/動脈硬化関連血管障害リスクの低減を目的とした自己脂肪組織由来幹細胞治療</v>
-      </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B16" s="14" t="s">
-        <v>144</v>
-      </c>
-      <c r="C16" s="15" t="s">
+      <c r="B7" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="D16" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>2種幹細胞/全般/自己脂肪由来幹細胞を用いた慢性疼痛治療</v>
-      </c>
-    </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B17" s="14" t="s">
+      <c r="C7" s="1" t="s">
         <v>147</v>
       </c>
-      <c r="C17" s="15" t="s">
+      <c r="D7" s="1" t="s">
         <v>148</v>
       </c>
-      <c r="D17" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>2種幹細胞/脳外科/自己脂肪由来幹細胞を用いた脳血管障害治療</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4">
-      <c r="A18" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B18" s="14" t="s">
+      <c r="E7" s="50" t="s">
         <v>149</v>
       </c>
-      <c r="C18" s="15" t="s">
+    </row>
+    <row r="8" spans="1:5" ht="150" customHeight="1">
+      <c r="A8" s="13" t="s">
         <v>150</v>
       </c>
-      <c r="D18" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>2種幹細胞/婦人科/自己脂肪由来幹細胞を用いたフレイル治療</v>
-      </c>
-    </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B19" s="14" t="s">
-        <v>149</v>
-      </c>
-      <c r="C19" s="15" t="s">
+      <c r="B8" s="34" t="s">
         <v>151</v>
       </c>
-      <c r="D19" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>2種幹細胞/婦人科/自己脂肪由来幹細胞を用いた更年期障害治療</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B20" s="14" t="s">
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="50" t="s">
         <v>152</v>
       </c>
-      <c r="C20" s="15" t="s">
+    </row>
+    <row r="9" spans="1:5" ht="262.5" customHeight="1">
+      <c r="A9" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="B9" s="33" t="s">
         <v>153</v>
       </c>
-      <c r="D20" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>2種幹細胞/内科/自己脂肪由来幹細胞を用いた肝障害治療</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B21" s="14" t="s">
-        <v>152</v>
-      </c>
-      <c r="C21" s="15" t="s">
+      <c r="C9" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="D21" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>2種幹細胞/内科/自己脂肪由来幹細胞を用いた糖尿病治療</v>
-      </c>
-    </row>
-    <row r="22" spans="1:4">
-      <c r="A22" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B22" s="14" t="s">
-        <v>130</v>
-      </c>
-      <c r="C22" s="15" t="s">
+      <c r="D9" s="1" t="s">
         <v>155</v>
       </c>
-      <c r="D22" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>2種幹細胞/AGA/自己脂肪由来幹細胞を用いた毛髪組織の治療（局所投与）</v>
-      </c>
-    </row>
-    <row r="23" spans="1:4">
-      <c r="A23" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B23" s="14" t="s">
+      <c r="E9" s="50" t="s">
         <v>156</v>
       </c>
-      <c r="C23" s="15" t="s">
+    </row>
+    <row r="10" spans="1:5" ht="213.6" customHeight="1">
+      <c r="A10" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="B10" s="19">
+        <v>55</v>
+      </c>
+      <c r="C10" s="1" t="s">
         <v>157</v>
       </c>
-      <c r="D23" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>2種幹細胞/泌尿器科/自己脂肪由来幹細胞を用いたED（勃起不全）治療（局所投与）</v>
-      </c>
-    </row>
-    <row r="24" spans="1:4" ht="37.5" customHeight="1">
-      <c r="A24" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B24" s="14" t="s">
+      <c r="D10" s="1" t="s">
         <v>158</v>
       </c>
-      <c r="C24" s="17" t="s">
+      <c r="E10" s="50" t="s">
         <v>159</v>
       </c>
-      <c r="D24" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>2種幹細胞/皮膚/アトピー性皮膚炎患者の主症状に対する自己脂肪由来間葉系
-幹細胞による治療</v>
-      </c>
-    </row>
-    <row r="25" spans="1:4">
-      <c r="A25" s="14" t="s">
-        <v>137</v>
-      </c>
-      <c r="B25" s="14" t="s">
+    </row>
+    <row r="11" spans="1:5" ht="150" customHeight="1">
+      <c r="A11" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="C25" s="15" t="s">
+      <c r="B11" s="19">
+        <v>13.5</v>
+      </c>
+      <c r="C11" s="1" t="s">
         <v>161</v>
       </c>
-      <c r="D25" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v xml:space="preserve">2種幹細胞/免疫治療/自己脂肪（組織）由来間葉系幹細胞を用いた自己免疫疾患の治療 </v>
-      </c>
-    </row>
-    <row r="26" spans="1:4">
-      <c r="D26" s="16" t="str">
-        <f t="shared" si="0"/>
-        <v>//</v>
+      <c r="D11" s="1" t="s">
+        <v>162</v>
+      </c>
+      <c r="E11" s="50" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="150" customHeight="1">
+      <c r="A12" s="19" t="s">
+        <v>164</v>
+      </c>
+      <c r="B12" s="19"/>
+      <c r="C12" s="1" t="s">
+        <v>165</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="E12" s="50" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="A14" s="19" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="19" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="19" t="s">
+        <v>169</v>
       </c>
     </row>
   </sheetData>
@@ -3427,219 +3508,206 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
-    <tabColor theme="7" tint="0.59999389629810485"/>
+    <tabColor theme="5" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="43.1640625" style="14" customWidth="1"/>
-    <col min="2" max="2" width="22.4140625" style="14" customWidth="1"/>
-    <col min="3" max="3" width="55.5" style="14" customWidth="1"/>
-    <col min="4" max="4" width="60.08203125" style="14" customWidth="1"/>
-    <col min="5" max="5" width="47.4140625" customWidth="1"/>
+    <col min="1" max="1" width="35.8984375" style="35" customWidth="1"/>
+    <col min="2" max="2" width="10" style="35" customWidth="1"/>
+    <col min="3" max="3" width="31" style="35" customWidth="1"/>
+    <col min="4" max="4" width="27.3984375" style="35" customWidth="1"/>
+    <col min="5" max="5" width="12.09765625" style="35" customWidth="1"/>
+    <col min="6" max="6" width="17" style="35" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
-      <c r="E1" s="39" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5">
-      <c r="A2" s="19" t="s">
-        <v>163</v>
-      </c>
-      <c r="B2" s="19" t="s">
-        <v>164</v>
-      </c>
-      <c r="C2" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="D2" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="E2" s="13" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="3" spans="1:5" ht="332.5" customHeight="1">
-      <c r="A3" s="19" t="s">
-        <v>33</v>
-      </c>
-      <c r="B3" s="19">
-        <v>20</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>168</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>169</v>
-      </c>
-      <c r="E3" s="38" t="s">
+    <row r="1" spans="1:6">
+      <c r="A1" s="29" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="187.5" customHeight="1">
-      <c r="A4" s="19" t="s">
+      <c r="B1" s="29" t="s">
         <v>171</v>
       </c>
-      <c r="B4" s="19">
-        <v>11</v>
-      </c>
-      <c r="C4" s="1" t="s">
+      <c r="C1" s="29" t="s">
         <v>172</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D1" s="29" t="s">
         <v>173</v>
       </c>
-      <c r="E4" s="38" t="s">
+      <c r="E1" s="29" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" ht="187.5" customHeight="1">
-      <c r="A5" s="19" t="s">
+      <c r="F1" s="29" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="29" t="s">
+        <v>239</v>
+      </c>
+      <c r="B2" s="29" t="s">
         <v>175</v>
       </c>
-      <c r="B5" s="19">
-        <v>22</v>
-      </c>
-      <c r="C5" s="1" t="s">
+      <c r="C2" s="30" t="s">
         <v>176</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>173</v>
-      </c>
-      <c r="E5" s="38" t="s">
+      <c r="D2" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="E2" s="30" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" ht="206.25" customHeight="1">
-      <c r="A6" s="19" t="s">
+      <c r="F2" s="52" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="29" t="s">
         <v>178</v>
       </c>
-      <c r="B6" s="19">
-        <v>15</v>
-      </c>
-      <c r="C6" s="1" t="s">
+      <c r="B3" s="30" t="s">
         <v>179</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="C3" s="31" t="s">
         <v>180</v>
       </c>
-      <c r="E6" s="38" t="s">
+      <c r="D3" s="30" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" ht="206.25" customHeight="1">
-      <c r="A7" s="19" t="s">
+      <c r="E3" s="30" t="s">
         <v>182</v>
       </c>
-      <c r="B7" s="35" t="s">
+      <c r="F3" s="52"/>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="29" t="s">
         <v>183</v>
       </c>
-      <c r="C7" s="1" t="s">
+      <c r="B4" s="30" t="s">
         <v>184</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="C4" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="D4" s="30" t="s">
+        <v>181</v>
+      </c>
+      <c r="E4" s="30" t="s">
+        <v>182</v>
+      </c>
+      <c r="F4" s="52"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="29" t="s">
         <v>185</v>
       </c>
-      <c r="E7" s="38" t="s">
+      <c r="B5" s="30" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" ht="150" customHeight="1">
-      <c r="A8" s="13" t="s">
+      <c r="C5" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="B8" s="36" t="s">
+      <c r="D5" s="30"/>
+      <c r="E5" s="30" t="s">
         <v>188</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="38" t="s">
+      <c r="F5" s="52" t="s">
         <v>189</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="262.5" customHeight="1">
-      <c r="A9" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="B9" s="35" t="s">
+    <row r="6" spans="1:6">
+      <c r="A6" s="29" t="s">
+        <v>266</v>
+      </c>
+      <c r="B6" s="30" t="s">
         <v>190</v>
       </c>
-      <c r="C9" s="1" t="s">
+      <c r="C6" s="32"/>
+      <c r="D6" s="30" t="s">
+        <v>267</v>
+      </c>
+      <c r="F6" s="52"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="29" t="s">
         <v>191</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="B7" s="30" t="s">
         <v>192</v>
       </c>
-      <c r="E9" s="38" t="s">
+      <c r="C7" s="32"/>
+      <c r="D7" s="30"/>
+      <c r="E7" s="30" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" ht="213.65" customHeight="1">
-      <c r="A10" s="19" t="s">
-        <v>37</v>
-      </c>
-      <c r="B10" s="19">
-        <v>55</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="F7" s="52"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="29" t="s">
         <v>194</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="B8" s="30" t="s">
         <v>195</v>
       </c>
-      <c r="E10" s="38" t="s">
+      <c r="C8" s="32" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" ht="150" customHeight="1">
-      <c r="A11" s="19" t="s">
+      <c r="D8" s="30"/>
+      <c r="E8" s="30" t="s">
         <v>197</v>
       </c>
-      <c r="B11" s="19">
-        <v>13.5</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="F8" s="52" t="s">
         <v>198</v>
       </c>
-      <c r="D11" s="1" t="s">
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="E11" s="38" t="s">
+      <c r="B9" s="30" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" ht="150" customHeight="1">
-      <c r="A12" s="19" t="s">
+      <c r="C9" s="32" t="s">
         <v>201</v>
       </c>
-      <c r="B12" s="19"/>
-      <c r="C12" s="1" t="s">
+      <c r="D9" s="30"/>
+      <c r="E9" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="F9" s="52"/>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="E12" s="38" t="s">
+      <c r="B10" s="30" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="19" t="s">
+      <c r="C10" s="32"/>
+      <c r="D10" s="30"/>
+      <c r="E10" s="30"/>
+      <c r="F10" s="52"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="29" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="19" t="s">
+      <c r="B11" s="30" t="s">
         <v>206</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>207</v>
+      </c>
+      <c r="D11" s="30" t="s">
+        <v>208</v>
+      </c>
+      <c r="E11" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="F11" s="52" t="s">
+        <v>210</v>
       </c>
     </row>
   </sheetData>
@@ -3650,207 +3718,111 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <sheetPr>
-    <tabColor theme="5" tint="0.59999389629810485"/>
-  </sheetPr>
-  <dimension ref="A1:F11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A2:D14"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <cols>
-    <col min="1" max="1" width="35.9140625" style="37" customWidth="1"/>
-    <col min="2" max="2" width="10" style="37" customWidth="1"/>
-    <col min="3" max="3" width="31" style="37" customWidth="1"/>
-    <col min="4" max="4" width="27.4140625" style="37" customWidth="1"/>
-    <col min="5" max="5" width="12.08203125" style="37" customWidth="1"/>
-    <col min="6" max="6" width="17" style="37" customWidth="1"/>
+    <col min="1" max="2" width="40.59765625" customWidth="1"/>
+    <col min="3" max="3" width="23.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="B1" s="31" t="s">
-        <v>208</v>
-      </c>
-      <c r="C1" s="31" t="s">
-        <v>209</v>
-      </c>
-      <c r="D1" s="31" t="s">
-        <v>210</v>
-      </c>
-      <c r="E1" s="31" t="s">
+    <row r="2" spans="1:4">
+      <c r="A2" t="s">
         <v>211</v>
       </c>
-      <c r="F1" s="31" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2" s="31" t="s">
-        <v>281</v>
-      </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" t="s">
         <v>212</v>
       </c>
-      <c r="C2" s="32" t="s">
+      <c r="C2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="25" t="s">
         <v>213</v>
       </c>
-      <c r="D2" s="32" t="s">
-        <v>282</v>
-      </c>
-      <c r="E2" s="32" t="s">
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4" t="s">
         <v>214</v>
       </c>
-      <c r="F2" s="32" t="s">
+      <c r="B4" s="24"/>
+      <c r="C4" s="24"/>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="31" t="s">
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6" t="s">
         <v>216</v>
       </c>
-      <c r="B3" s="32" t="s">
+      <c r="B6" s="24"/>
+      <c r="C6" s="24"/>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7" t="s">
         <v>217</v>
       </c>
-      <c r="C3" s="33" t="s">
+      <c r="B7" s="24"/>
+      <c r="C7" s="24"/>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8" t="s">
         <v>218</v>
       </c>
-      <c r="D3" s="32" t="s">
+      <c r="B8" s="24"/>
+      <c r="C8" s="24"/>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9" t="s">
         <v>219</v>
       </c>
-      <c r="E3" s="32" t="s">
+      <c r="B9" s="24"/>
+      <c r="C9" s="24"/>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10" t="s">
         <v>220</v>
       </c>
-      <c r="F3" s="32"/>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="31" t="s">
+      <c r="B10" s="24"/>
+      <c r="C10" s="24"/>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11" t="s">
         <v>221</v>
       </c>
-      <c r="B4" s="32" t="s">
+      <c r="B11" s="24"/>
+      <c r="C11" s="24"/>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12" t="s">
         <v>222</v>
       </c>
-      <c r="C4" s="34" t="s">
-        <v>218</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>219</v>
-      </c>
-      <c r="E4" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="F4" s="32"/>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="31" t="s">
+      <c r="B12" s="24"/>
+      <c r="C12" s="24"/>
+    </row>
+    <row r="13" spans="1:4">
+      <c r="A13" t="s">
         <v>223</v>
       </c>
-      <c r="B5" s="32" t="s">
+      <c r="B13" s="24"/>
+      <c r="C13" s="24"/>
+    </row>
+    <row r="14" spans="1:4">
+      <c r="A14" t="s">
         <v>224</v>
       </c>
-      <c r="C5" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="D5" s="32"/>
-      <c r="E5" s="32" t="s">
-        <v>226</v>
-      </c>
-      <c r="F5" s="32" t="s">
-        <v>227</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="31" t="s">
-        <v>311</v>
-      </c>
-      <c r="B6" s="32" t="s">
-        <v>229</v>
-      </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="32" t="s">
-        <v>312</v>
-      </c>
-      <c r="F6" s="32"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="31" t="s">
-        <v>231</v>
-      </c>
-      <c r="B7" s="32" t="s">
-        <v>232</v>
-      </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="32"/>
-      <c r="E7" s="32" t="s">
-        <v>233</v>
-      </c>
-      <c r="F7" s="32"/>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="31" t="s">
-        <v>234</v>
-      </c>
-      <c r="B8" s="32" t="s">
-        <v>235</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>236</v>
-      </c>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32" t="s">
-        <v>237</v>
-      </c>
-      <c r="F8" s="32" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="31" t="s">
-        <v>239</v>
-      </c>
-      <c r="B9" s="32" t="s">
-        <v>240</v>
-      </c>
-      <c r="C9" s="34" t="s">
-        <v>241</v>
-      </c>
-      <c r="D9" s="32"/>
-      <c r="E9" s="32" t="s">
-        <v>242</v>
-      </c>
-      <c r="F9" s="32"/>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="31" t="s">
-        <v>243</v>
-      </c>
-      <c r="B10" s="32" t="s">
-        <v>244</v>
-      </c>
-      <c r="C10" s="34"/>
-      <c r="D10" s="32"/>
-      <c r="E10" s="32"/>
-      <c r="F10" s="32"/>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="31" t="s">
-        <v>245</v>
-      </c>
-      <c r="B11" s="32" t="s">
-        <v>246</v>
-      </c>
-      <c r="C11" s="34" t="s">
-        <v>247</v>
-      </c>
-      <c r="D11" s="32" t="s">
-        <v>248</v>
-      </c>
-      <c r="E11" s="32" t="s">
-        <v>249</v>
-      </c>
-      <c r="F11" s="32" t="s">
-        <v>250</v>
-      </c>
+      <c r="B14" s="24"/>
+      <c r="C14" s="24"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1"/>
@@ -3860,121 +3832,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A2:D14"/>
-  <sheetFormatPr defaultRowHeight="18"/>
-  <cols>
-    <col min="1" max="2" width="40.58203125" customWidth="1"/>
-    <col min="3" max="3" width="23.5" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:4">
-      <c r="A2" t="s">
-        <v>251</v>
-      </c>
-      <c r="B2" t="s">
-        <v>252</v>
-      </c>
-      <c r="C2" t="s">
-        <v>81</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B3" s="26"/>
-      <c r="C3" s="26"/>
-      <c r="D3" s="27" t="s">
-        <v>253</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4" t="s">
-        <v>254</v>
-      </c>
-      <c r="B4" s="26"/>
-      <c r="C4" s="26"/>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5" t="s">
-        <v>255</v>
-      </c>
-      <c r="B5" s="26"/>
-      <c r="C5" s="26"/>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6" t="s">
-        <v>256</v>
-      </c>
-      <c r="B6" s="26"/>
-      <c r="C6" s="26"/>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7" t="s">
-        <v>257</v>
-      </c>
-      <c r="B7" s="26"/>
-      <c r="C7" s="26"/>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" t="s">
-        <v>258</v>
-      </c>
-      <c r="B8" s="26"/>
-      <c r="C8" s="26"/>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9" t="s">
-        <v>259</v>
-      </c>
-      <c r="B9" s="26"/>
-      <c r="C9" s="26"/>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" t="s">
-        <v>260</v>
-      </c>
-      <c r="B10" s="26"/>
-      <c r="C10" s="26"/>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11" t="s">
-        <v>261</v>
-      </c>
-      <c r="B11" s="26"/>
-      <c r="C11" s="26"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" t="s">
-        <v>262</v>
-      </c>
-      <c r="B12" s="26"/>
-      <c r="C12" s="26"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" t="s">
-        <v>263</v>
-      </c>
-      <c r="B13" s="26"/>
-      <c r="C13" s="26"/>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" t="s">
-        <v>264</v>
-      </c>
-      <c r="B14" s="26"/>
-      <c r="C14" s="26"/>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1"/>
   <sheetFormatPr defaultRowHeight="18"/>
   <sheetData/>
